--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetTypeSetting001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetTypeSetting001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>资产一级分类</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -27,10 +27,6 @@
   </si>
   <si>
     <t>资产三级分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>业务分类</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -389,15 +385,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="4" max="4" width="30.77734375" customWidth="1"/>
+    <col min="1" max="1" width="21.875" customWidth="1"/>
+    <col min="2" max="2" width="19.625" customWidth="1"/>
+    <col min="3" max="3" width="22.125" customWidth="1"/>
+    <col min="4" max="4" width="30.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -407,9 +403,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="D1" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -421,7 +415,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -431,7 +425,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetTypeSetting001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/AssetTypeSetting001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>资产一级分类</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -28,6 +28,14 @@
   <si>
     <t>资产三级分类</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产/负债类别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产/负债二级类别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -52,6 +60,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -384,16 +393,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="21.875" customWidth="1"/>
     <col min="2" max="2" width="19.625" customWidth="1"/>
     <col min="3" max="3" width="22.125" customWidth="1"/>
-    <col min="4" max="4" width="30.75" customWidth="1"/>
+    <col min="4" max="4" width="34.875" customWidth="1"/>
+    <col min="5" max="5" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -403,7 +413,12 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
